--- a/Assets/Data/Excel/TimeSpawnConfig.xlsx
+++ b/Assets/Data/Excel/TimeSpawnConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\2DModulePlay\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AEB21D9-171E-467F-9F7B-9E95016FCC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA5A8586-6FB9-4403-AC5A-3E9C44E2FFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17865" yWindow="4635" windowWidth="13395" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29235" yWindow="11730" windowWidth="13395" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>Id</t>
   </si>
@@ -408,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="12.5" style="1"/>
@@ -474,7 +474,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -492,6 +492,26 @@
       </c>
       <c r="F4" s="1">
         <v>0.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1">
+        <v>102</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Excel/TimeSpawnConfig.xlsx
+++ b/Assets/Data/Excel/TimeSpawnConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\2DModulePlay\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA5A8586-6FB9-4403-AC5A-3E9C44E2FFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1354C617-B1D6-47FA-AC52-620DDE623AAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29235" yWindow="11730" windowWidth="13395" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
   <si>
     <t>Id</t>
   </si>
@@ -408,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="12.5" style="1"/>
@@ -482,7 +482,7 @@
         <v>101</v>
       </c>
       <c r="C4" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>16</v>
@@ -511,6 +511,66 @@
         <v>0.5</v>
       </c>
       <c r="F5" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1">
+        <v>103</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1">
+        <v>104</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1">
+        <v>105</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="1">
         <v>0.5</v>
       </c>
     </row>
